--- a/datasets/day1_excel_foundations/05_functions_and_data_tips/practice_start.xlsx
+++ b/datasets/day1_excel_foundations/05_functions_and_data_tips/practice_start.xlsx
@@ -476,8 +476,8 @@
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="16.5" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="19.5" customWidth="1" min="3" max="3"/>
+    <col width="10.5" customWidth="1" min="4" max="4"/>
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
@@ -549,12 +549,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -591,12 +591,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -927,12 +927,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>US Sales</t>
+          <t>Zimbabwe Sales</t>
         </is>
       </c>
       <c r="L11" s="7" t="n"/>
@@ -969,12 +969,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sofia Lopez</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1862,7 +1862,7 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>STEP 6 - One more condition.  L11:  =SUMIF(D2:D31,"United States",H2:H31)</t>
+          <t>STEP 6 - One more condition.  L11:  =SUMIF(D2:D31,"Zimbabwe",H2:H31)</t>
         </is>
       </c>
     </row>
